--- a/sipii_caixa_20260724.xlsx
+++ b/sipii_caixa_20260724.xlsx
@@ -14343,42 +14343,182 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
-      <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr"/>
-      <c r="AE54" s="2" t="inlineStr"/>
-      <c r="AF54" s="2" t="inlineStr"/>
-      <c r="AG54" s="2" t="inlineStr"/>
-      <c r="AH54" s="2" t="inlineStr"/>
-      <c r="AI54" s="2" t="inlineStr"/>
-      <c r="AJ54" s="2" t="inlineStr"/>
-      <c r="AK54" s="2" t="inlineStr"/>
-      <c r="AL54" s="2" t="inlineStr"/>
-      <c r="AM54" s="2" t="inlineStr"/>
-      <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Curto Prazo</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>CURTO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
-      <c r="AQ54" s="2" t="inlineStr"/>
-      <c r="AR54" s="2" t="inlineStr"/>
-      <c r="AS54" s="2" t="inlineStr"/>
-      <c r="AT54" s="2" t="inlineStr"/>
-      <c r="AU54" s="2" t="inlineStr"/>
-      <c r="AV54" s="2" t="inlineStr"/>
-      <c r="AW54" s="2" t="inlineStr"/>
-      <c r="AX54" s="2" t="inlineStr"/>
-      <c r="AY54" s="2" t="inlineStr"/>
-      <c r="AZ54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR54" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS54" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AT54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AU54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AV54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AW54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AX54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AY54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AZ54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
+        </is>
+      </c>
       <c r="BA54" s="2" t="inlineStr"/>
       <c r="BB54" s="2" t="inlineStr"/>
     </row>
